--- a/Corpora/Main Corpus/main_corpus_batch_tracker.xlsx
+++ b/Corpora/Main Corpus/main_corpus_batch_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8499219-4E6D-4B01-9B4D-56059B30123A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8FD0A-ADF2-4E9B-B6C1-5688EDFF6911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Batch_Tracker" sheetId="1" r:id="rId1"/>
     <sheet name="Setup" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="339">
   <si>
     <t>Main Corpus Batch Tracker (2013–2025)</t>
   </si>
@@ -65,9 +78,6 @@
     <t>2013-01</t>
   </si>
   <si>
-    <t>not_started</t>
-  </si>
-  <si>
     <t>M201302</t>
   </si>
   <si>
@@ -1035,6 +1045,12 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>скачал с render галкой</t>
+  </si>
+  <si>
+    <t>Очень много DROP</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1085,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1086,6 +1102,18 @@
         <fgColor rgb="FFEAF2F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1099,7 +1127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1112,6 +1140,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1120,6 +1150,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1287,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -1301,32 +1334,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
     </row>
     <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1376,17 +1409,15 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="H5" s="3">
-        <v>42</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
         <v>41306</v>
@@ -1395,12 +1426,12 @@
         <v>41333</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -1408,7 +1439,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
         <v>41334</v>
@@ -1417,12 +1448,12 @@
         <v>41364</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -1430,7 +1461,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
         <v>41365</v>
@@ -1439,12 +1470,12 @@
         <v>41394</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -1452,7 +1483,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2">
         <v>41395</v>
@@ -1461,12 +1492,12 @@
         <v>41425</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1474,7 +1505,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2">
         <v>41426</v>
@@ -1483,12 +1514,12 @@
         <v>41455</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -1496,7 +1527,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>41456</v>
@@ -1505,12 +1536,12 @@
         <v>41486</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -1518,7 +1549,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2">
         <v>41487</v>
@@ -1527,12 +1558,12 @@
         <v>41517</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -1540,7 +1571,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
         <v>41518</v>
@@ -1549,12 +1580,12 @@
         <v>41547</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -1562,7 +1593,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2">
         <v>41548</v>
@@ -1571,12 +1602,12 @@
         <v>41578</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -1584,7 +1615,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
         <v>41579</v>
@@ -1593,12 +1624,12 @@
         <v>41608</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -1606,7 +1637,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>41609</v>
@@ -1615,12 +1646,12 @@
         <v>41639</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -1628,7 +1659,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
         <v>41640</v>
@@ -1637,12 +1668,12 @@
         <v>41670</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1650,7 +1681,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
         <v>41671</v>
@@ -1659,12 +1690,12 @@
         <v>41698</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1672,7 +1703,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
         <v>41699</v>
@@ -1681,12 +1712,12 @@
         <v>41729</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -1694,7 +1725,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2">
         <v>41730</v>
@@ -1703,12 +1734,12 @@
         <v>41759</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -1716,7 +1747,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2">
         <v>41760</v>
@@ -1725,12 +1756,12 @@
         <v>41790</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1738,7 +1769,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2">
         <v>41791</v>
@@ -1747,12 +1778,12 @@
         <v>41820</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -1760,7 +1791,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2">
         <v>41821</v>
@@ -1769,12 +1800,12 @@
         <v>41851</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -1782,7 +1813,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2">
         <v>41852</v>
@@ -1791,12 +1822,12 @@
         <v>41882</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -1804,7 +1835,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2">
         <v>41883</v>
@@ -1813,12 +1844,12 @@
         <v>41912</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -1826,7 +1857,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2">
         <v>41913</v>
@@ -1835,12 +1866,12 @@
         <v>41943</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -1848,7 +1879,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2">
         <v>41944</v>
@@ -1857,12 +1888,12 @@
         <v>41973</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -1870,7 +1901,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2">
         <v>41974</v>
@@ -1879,12 +1910,12 @@
         <v>42004</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -1892,7 +1923,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2">
         <v>42005</v>
@@ -1901,12 +1932,12 @@
         <v>42035</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -1914,7 +1945,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2">
         <v>42036</v>
@@ -1923,12 +1954,12 @@
         <v>42063</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -1936,7 +1967,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2">
         <v>42064</v>
@@ -1945,12 +1976,12 @@
         <v>42094</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -1958,7 +1989,7 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2">
         <v>42095</v>
@@ -1967,12 +1998,12 @@
         <v>42124</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -1980,7 +2011,7 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2">
         <v>42125</v>
@@ -1989,12 +2020,12 @@
         <v>42155</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2002,7 +2033,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B34" s="2">
         <v>42156</v>
@@ -2011,12 +2042,12 @@
         <v>42185</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -2024,7 +2055,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35" s="2">
         <v>42186</v>
@@ -2033,20 +2064,22 @@
         <v>42216</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" s="2">
         <v>42217</v>
@@ -2055,12 +2088,12 @@
         <v>42247</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -2068,7 +2101,7 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="2">
         <v>42248</v>
@@ -2077,12 +2110,12 @@
         <v>42277</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -2090,7 +2123,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B38" s="2">
         <v>42278</v>
@@ -2099,12 +2132,12 @@
         <v>42308</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2112,7 +2145,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="2">
         <v>42309</v>
@@ -2121,12 +2154,12 @@
         <v>42338</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2134,7 +2167,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B40" s="2">
         <v>42339</v>
@@ -2143,12 +2176,12 @@
         <v>42369</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -2156,7 +2189,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B41" s="2">
         <v>42370</v>
@@ -2165,12 +2198,12 @@
         <v>42400</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -2178,7 +2211,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B42" s="2">
         <v>42401</v>
@@ -2187,12 +2220,12 @@
         <v>42429</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -2200,7 +2233,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="2">
         <v>42430</v>
@@ -2209,12 +2242,12 @@
         <v>42460</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -2222,7 +2255,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B44" s="2">
         <v>42461</v>
@@ -2231,12 +2264,12 @@
         <v>42490</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -2244,7 +2277,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="2">
         <v>42491</v>
@@ -2253,12 +2286,12 @@
         <v>42521</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -2266,7 +2299,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" s="2">
         <v>42522</v>
@@ -2275,12 +2308,12 @@
         <v>42551</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -2288,7 +2321,7 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2">
         <v>42552</v>
@@ -2297,12 +2330,12 @@
         <v>42582</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -2310,7 +2343,7 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B48" s="2">
         <v>42583</v>
@@ -2319,12 +2352,12 @@
         <v>42613</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -2332,7 +2365,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2">
         <v>42614</v>
@@ -2341,12 +2374,12 @@
         <v>42643</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -2354,7 +2387,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2">
         <v>42644</v>
@@ -2363,12 +2396,12 @@
         <v>42674</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -2376,7 +2409,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" s="2">
         <v>42675</v>
@@ -2385,12 +2418,12 @@
         <v>42704</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -2398,7 +2431,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B52" s="2">
         <v>42705</v>
@@ -2407,12 +2440,12 @@
         <v>42735</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -2420,7 +2453,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B53" s="2">
         <v>42736</v>
@@ -2429,12 +2462,12 @@
         <v>42766</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -2442,7 +2475,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B54" s="2">
         <v>42767</v>
@@ -2451,12 +2484,12 @@
         <v>42794</v>
       </c>
       <c r="D54" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -2464,7 +2497,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B55" s="2">
         <v>42795</v>
@@ -2473,12 +2506,12 @@
         <v>42825</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -2486,7 +2519,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B56" s="2">
         <v>42826</v>
@@ -2495,12 +2528,12 @@
         <v>42855</v>
       </c>
       <c r="D56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -2508,7 +2541,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B57" s="2">
         <v>42856</v>
@@ -2517,12 +2550,12 @@
         <v>42886</v>
       </c>
       <c r="D57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -2530,7 +2563,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B58" s="2">
         <v>42887</v>
@@ -2539,12 +2572,12 @@
         <v>42916</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -2552,7 +2585,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B59" s="2">
         <v>42917</v>
@@ -2561,12 +2594,12 @@
         <v>42947</v>
       </c>
       <c r="D59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -2574,7 +2607,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B60" s="2">
         <v>42948</v>
@@ -2583,12 +2616,12 @@
         <v>42978</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2596,7 +2629,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B61" s="2">
         <v>42979</v>
@@ -2605,12 +2638,12 @@
         <v>43008</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2618,7 +2651,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B62" s="2">
         <v>43009</v>
@@ -2627,12 +2660,12 @@
         <v>43039</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -2640,7 +2673,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B63" s="2">
         <v>43040</v>
@@ -2649,12 +2682,12 @@
         <v>43069</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -2662,7 +2695,7 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B64" s="2">
         <v>43070</v>
@@ -2671,12 +2704,12 @@
         <v>43100</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2684,7 +2717,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B65" s="2">
         <v>43101</v>
@@ -2693,12 +2726,12 @@
         <v>43131</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -2706,7 +2739,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B66" s="2">
         <v>43132</v>
@@ -2715,12 +2748,12 @@
         <v>43159</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -2728,7 +2761,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B67" s="2">
         <v>43160</v>
@@ -2737,12 +2770,12 @@
         <v>43190</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
@@ -2750,7 +2783,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B68" s="2">
         <v>43191</v>
@@ -2759,12 +2792,12 @@
         <v>43220</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -2772,7 +2805,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B69" s="2">
         <v>43221</v>
@@ -2781,12 +2814,12 @@
         <v>43251</v>
       </c>
       <c r="D69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -2794,7 +2827,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B70" s="2">
         <v>43252</v>
@@ -2803,12 +2836,12 @@
         <v>43281</v>
       </c>
       <c r="D70" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -2816,7 +2849,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B71" s="2">
         <v>43282</v>
@@ -2825,12 +2858,12 @@
         <v>43312</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -2838,7 +2871,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B72" s="2">
         <v>43313</v>
@@ -2847,12 +2880,12 @@
         <v>43343</v>
       </c>
       <c r="D72" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -2860,7 +2893,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B73" s="2">
         <v>43344</v>
@@ -2869,12 +2902,12 @@
         <v>43373</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -2882,7 +2915,7 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B74" s="2">
         <v>43374</v>
@@ -2891,20 +2924,22 @@
         <v>43404</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
-      <c r="J74" s="4"/>
+      <c r="J74" s="12" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B75" s="2">
         <v>43405</v>
@@ -2913,20 +2948,20 @@
         <v>43434</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
-      <c r="J75" s="4"/>
+      <c r="J75" s="12"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B76" s="2">
         <v>43435</v>
@@ -2935,20 +2970,20 @@
         <v>43465</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
-      <c r="J76" s="4"/>
+      <c r="J76" s="12"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B77" s="2">
         <v>43466</v>
@@ -2957,20 +2992,20 @@
         <v>43496</v>
       </c>
       <c r="D77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
-      <c r="J77" s="4"/>
+      <c r="J77" s="12"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B78" s="2">
         <v>43497</v>
@@ -2979,12 +3014,12 @@
         <v>43524</v>
       </c>
       <c r="D78" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
@@ -2992,7 +3027,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B79" s="2">
         <v>43525</v>
@@ -3001,12 +3036,12 @@
         <v>43555</v>
       </c>
       <c r="D79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -3014,7 +3049,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B80" s="2">
         <v>43556</v>
@@ -3023,12 +3058,12 @@
         <v>43585</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
@@ -3036,7 +3071,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B81" s="2">
         <v>43586</v>
@@ -3045,12 +3080,12 @@
         <v>43616</v>
       </c>
       <c r="D81" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
@@ -3058,7 +3093,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B82" s="2">
         <v>43617</v>
@@ -3067,12 +3102,12 @@
         <v>43646</v>
       </c>
       <c r="D82" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
       <c r="G82" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
@@ -3080,7 +3115,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B83" s="2">
         <v>43647</v>
@@ -3089,12 +3124,12 @@
         <v>43677</v>
       </c>
       <c r="D83" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
@@ -3102,7 +3137,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B84" s="2">
         <v>43678</v>
@@ -3111,12 +3146,12 @@
         <v>43708</v>
       </c>
       <c r="D84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
@@ -3124,7 +3159,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B85" s="2">
         <v>43709</v>
@@ -3133,12 +3168,12 @@
         <v>43738</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
@@ -3146,7 +3181,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B86" s="2">
         <v>43739</v>
@@ -3155,12 +3190,12 @@
         <v>43769</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
@@ -3168,7 +3203,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B87" s="2">
         <v>43770</v>
@@ -3177,12 +3212,12 @@
         <v>43799</v>
       </c>
       <c r="D87" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
@@ -3190,7 +3225,7 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B88" s="2">
         <v>43800</v>
@@ -3199,12 +3234,12 @@
         <v>43830</v>
       </c>
       <c r="D88" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
@@ -3212,7 +3247,7 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B89" s="2">
         <v>43831</v>
@@ -3221,12 +3256,12 @@
         <v>43861</v>
       </c>
       <c r="D89" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
@@ -3234,7 +3269,7 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B90" s="2">
         <v>43862</v>
@@ -3243,12 +3278,12 @@
         <v>43890</v>
       </c>
       <c r="D90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
@@ -3256,7 +3291,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B91" s="2">
         <v>43891</v>
@@ -3265,12 +3300,12 @@
         <v>43921</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
@@ -3278,7 +3313,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B92" s="2">
         <v>43922</v>
@@ -3287,12 +3322,12 @@
         <v>43951</v>
       </c>
       <c r="D92" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
@@ -3300,7 +3335,7 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B93" s="2">
         <v>43952</v>
@@ -3309,12 +3344,12 @@
         <v>43982</v>
       </c>
       <c r="D93" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
@@ -3322,7 +3357,7 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B94" s="2">
         <v>43983</v>
@@ -3331,12 +3366,12 @@
         <v>44012</v>
       </c>
       <c r="D94" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
@@ -3344,7 +3379,7 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B95" s="2">
         <v>44013</v>
@@ -3353,12 +3388,12 @@
         <v>44043</v>
       </c>
       <c r="D95" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
@@ -3366,7 +3401,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B96" s="2">
         <v>44044</v>
@@ -3375,12 +3410,12 @@
         <v>44074</v>
       </c>
       <c r="D96" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
@@ -3388,7 +3423,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B97" s="2">
         <v>44075</v>
@@ -3397,12 +3432,12 @@
         <v>44104</v>
       </c>
       <c r="D97" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
@@ -3410,7 +3445,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B98" s="2">
         <v>44105</v>
@@ -3419,12 +3454,12 @@
         <v>44135</v>
       </c>
       <c r="D98" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
@@ -3432,7 +3467,7 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B99" s="2">
         <v>44136</v>
@@ -3441,12 +3476,12 @@
         <v>44165</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
@@ -3454,7 +3489,7 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B100" s="2">
         <v>44166</v>
@@ -3463,12 +3498,12 @@
         <v>44196</v>
       </c>
       <c r="D100" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
@@ -3476,7 +3511,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B101" s="2">
         <v>44197</v>
@@ -3485,12 +3520,12 @@
         <v>44227</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
@@ -3498,7 +3533,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B102" s="2">
         <v>44228</v>
@@ -3507,12 +3542,12 @@
         <v>44255</v>
       </c>
       <c r="D102" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
@@ -3520,7 +3555,7 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B103" s="2">
         <v>44256</v>
@@ -3529,12 +3564,12 @@
         <v>44286</v>
       </c>
       <c r="D103" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
@@ -3542,7 +3577,7 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B104" s="2">
         <v>44287</v>
@@ -3551,12 +3586,12 @@
         <v>44316</v>
       </c>
       <c r="D104" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="G104" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
@@ -3564,7 +3599,7 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B105" s="2">
         <v>44317</v>
@@ -3573,12 +3608,12 @@
         <v>44347</v>
       </c>
       <c r="D105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
@@ -3586,7 +3621,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B106" s="2">
         <v>44348</v>
@@ -3595,12 +3630,12 @@
         <v>44377</v>
       </c>
       <c r="D106" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="G106" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
@@ -3608,7 +3643,7 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B107" s="2">
         <v>44378</v>
@@ -3617,12 +3652,12 @@
         <v>44408</v>
       </c>
       <c r="D107" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
@@ -3630,7 +3665,7 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B108" s="2">
         <v>44409</v>
@@ -3639,12 +3674,12 @@
         <v>44439</v>
       </c>
       <c r="D108" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
@@ -3652,7 +3687,7 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B109" s="2">
         <v>44440</v>
@@ -3661,12 +3696,12 @@
         <v>44469</v>
       </c>
       <c r="D109" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="G109" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="3"/>
@@ -3674,7 +3709,7 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B110" s="2">
         <v>44470</v>
@@ -3683,12 +3718,12 @@
         <v>44500</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
@@ -3696,7 +3731,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B111" s="2">
         <v>44501</v>
@@ -3705,12 +3740,12 @@
         <v>44530</v>
       </c>
       <c r="D111" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
@@ -3718,7 +3753,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B112" s="2">
         <v>44531</v>
@@ -3727,12 +3762,12 @@
         <v>44561</v>
       </c>
       <c r="D112" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
@@ -3740,7 +3775,7 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B113" s="2">
         <v>44562</v>
@@ -3749,12 +3784,12 @@
         <v>44592</v>
       </c>
       <c r="D113" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="G113" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
@@ -3762,7 +3797,7 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B114" s="2">
         <v>44593</v>
@@ -3771,12 +3806,12 @@
         <v>44620</v>
       </c>
       <c r="D114" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="3"/>
@@ -3784,7 +3819,7 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B115" s="2">
         <v>44621</v>
@@ -3793,12 +3828,12 @@
         <v>44651</v>
       </c>
       <c r="D115" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
@@ -3806,7 +3841,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B116" s="2">
         <v>44652</v>
@@ -3815,12 +3850,12 @@
         <v>44681</v>
       </c>
       <c r="D116" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
@@ -3828,7 +3863,7 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B117" s="2">
         <v>44682</v>
@@ -3837,12 +3872,12 @@
         <v>44712</v>
       </c>
       <c r="D117" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
@@ -3850,7 +3885,7 @@
     </row>
     <row r="118" spans="1:10">
       <c r="A118" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B118" s="2">
         <v>44713</v>
@@ -3859,12 +3894,12 @@
         <v>44742</v>
       </c>
       <c r="D118" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
@@ -3872,7 +3907,7 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B119" s="2">
         <v>44743</v>
@@ -3881,12 +3916,12 @@
         <v>44773</v>
       </c>
       <c r="D119" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
@@ -3894,7 +3929,7 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B120" s="2">
         <v>44774</v>
@@ -3903,12 +3938,12 @@
         <v>44804</v>
       </c>
       <c r="D120" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="G120" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
@@ -3916,7 +3951,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B121" s="2">
         <v>44805</v>
@@ -3925,12 +3960,12 @@
         <v>44834</v>
       </c>
       <c r="D121" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
       <c r="G121" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
@@ -3938,7 +3973,7 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B122" s="2">
         <v>44835</v>
@@ -3947,12 +3982,12 @@
         <v>44865</v>
       </c>
       <c r="D122" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="G122" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
@@ -3960,7 +3995,7 @@
     </row>
     <row r="123" spans="1:10">
       <c r="A123" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B123" s="2">
         <v>44866</v>
@@ -3969,12 +4004,12 @@
         <v>44895</v>
       </c>
       <c r="D123" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
@@ -3982,7 +4017,7 @@
     </row>
     <row r="124" spans="1:10">
       <c r="A124" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B124" s="2">
         <v>44896</v>
@@ -3991,12 +4026,12 @@
         <v>44926</v>
       </c>
       <c r="D124" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
       <c r="G124" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
@@ -4004,7 +4039,7 @@
     </row>
     <row r="125" spans="1:10">
       <c r="A125" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B125" s="2">
         <v>44927</v>
@@ -4013,12 +4048,12 @@
         <v>44957</v>
       </c>
       <c r="D125" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H125" s="3"/>
       <c r="I125" s="3"/>
@@ -4026,7 +4061,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B126" s="2">
         <v>44958</v>
@@ -4035,12 +4070,12 @@
         <v>44985</v>
       </c>
       <c r="D126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="G126" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
@@ -4048,7 +4083,7 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B127" s="2">
         <v>44986</v>
@@ -4057,12 +4092,12 @@
         <v>45016</v>
       </c>
       <c r="D127" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
@@ -4070,7 +4105,7 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B128" s="2">
         <v>45017</v>
@@ -4079,12 +4114,12 @@
         <v>45046</v>
       </c>
       <c r="D128" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
@@ -4092,7 +4127,7 @@
     </row>
     <row r="129" spans="1:10">
       <c r="A129" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B129" s="2">
         <v>45047</v>
@@ -4101,12 +4136,12 @@
         <v>45077</v>
       </c>
       <c r="D129" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H129" s="3"/>
       <c r="I129" s="3"/>
@@ -4114,7 +4149,7 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B130" s="2">
         <v>45078</v>
@@ -4123,12 +4158,12 @@
         <v>45107</v>
       </c>
       <c r="D130" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
@@ -4136,7 +4171,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B131" s="2">
         <v>45108</v>
@@ -4145,12 +4180,12 @@
         <v>45138</v>
       </c>
       <c r="D131" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
@@ -4158,7 +4193,7 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B132" s="2">
         <v>45139</v>
@@ -4167,12 +4202,12 @@
         <v>45169</v>
       </c>
       <c r="D132" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
       <c r="G132" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
@@ -4180,7 +4215,7 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B133" s="2">
         <v>45170</v>
@@ -4189,12 +4224,12 @@
         <v>45199</v>
       </c>
       <c r="D133" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="G133" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
@@ -4202,7 +4237,7 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B134" s="2">
         <v>45200</v>
@@ -4211,12 +4246,12 @@
         <v>45230</v>
       </c>
       <c r="D134" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
@@ -4224,7 +4259,7 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B135" s="2">
         <v>45231</v>
@@ -4233,12 +4268,12 @@
         <v>45260</v>
       </c>
       <c r="D135" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
@@ -4246,7 +4281,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B136" s="2">
         <v>45261</v>
@@ -4255,12 +4290,12 @@
         <v>45291</v>
       </c>
       <c r="D136" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="G136" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
@@ -4268,7 +4303,7 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B137" s="2">
         <v>45292</v>
@@ -4277,12 +4312,12 @@
         <v>45322</v>
       </c>
       <c r="D137" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="3"/>
@@ -4290,7 +4325,7 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B138" s="2">
         <v>45323</v>
@@ -4299,12 +4334,12 @@
         <v>45351</v>
       </c>
       <c r="D138" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H138" s="3"/>
       <c r="I138" s="3"/>
@@ -4312,7 +4347,7 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B139" s="2">
         <v>45352</v>
@@ -4321,12 +4356,12 @@
         <v>45382</v>
       </c>
       <c r="D139" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
       <c r="G139" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H139" s="3"/>
       <c r="I139" s="3"/>
@@ -4334,7 +4369,7 @@
     </row>
     <row r="140" spans="1:10">
       <c r="A140" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B140" s="2">
         <v>45383</v>
@@ -4343,12 +4378,12 @@
         <v>45412</v>
       </c>
       <c r="D140" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
       <c r="G140" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H140" s="3"/>
       <c r="I140" s="3"/>
@@ -4356,7 +4391,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B141" s="2">
         <v>45413</v>
@@ -4365,12 +4400,12 @@
         <v>45443</v>
       </c>
       <c r="D141" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
       <c r="G141" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
@@ -4378,7 +4413,7 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B142" s="2">
         <v>45444</v>
@@ -4387,12 +4422,12 @@
         <v>45473</v>
       </c>
       <c r="D142" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="G142" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
@@ -4400,7 +4435,7 @@
     </row>
     <row r="143" spans="1:10">
       <c r="A143" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B143" s="2">
         <v>45474</v>
@@ -4409,12 +4444,12 @@
         <v>45504</v>
       </c>
       <c r="D143" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H143" s="3"/>
       <c r="I143" s="3"/>
@@ -4422,7 +4457,7 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B144" s="2">
         <v>45505</v>
@@ -4431,12 +4466,12 @@
         <v>45535</v>
       </c>
       <c r="D144" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
@@ -4444,7 +4479,7 @@
     </row>
     <row r="145" spans="1:10">
       <c r="A145" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B145" s="2">
         <v>45536</v>
@@ -4453,12 +4488,12 @@
         <v>45565</v>
       </c>
       <c r="D145" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H145" s="3"/>
       <c r="I145" s="3"/>
@@ -4466,7 +4501,7 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B146" s="2">
         <v>45566</v>
@@ -4475,12 +4510,12 @@
         <v>45596</v>
       </c>
       <c r="D146" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
@@ -4488,7 +4523,7 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B147" s="2">
         <v>45597</v>
@@ -4497,12 +4532,12 @@
         <v>45626</v>
       </c>
       <c r="D147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H147" s="3"/>
       <c r="I147" s="3"/>
@@ -4510,7 +4545,7 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B148" s="2">
         <v>45627</v>
@@ -4519,12 +4554,12 @@
         <v>45657</v>
       </c>
       <c r="D148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
       <c r="G148" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
@@ -4532,7 +4567,7 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B149" s="2">
         <v>45658</v>
@@ -4541,12 +4576,12 @@
         <v>45688</v>
       </c>
       <c r="D149" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
       <c r="G149" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
@@ -4554,7 +4589,7 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B150" s="2">
         <v>45689</v>
@@ -4563,12 +4598,12 @@
         <v>45716</v>
       </c>
       <c r="D150" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="G150" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
@@ -4576,7 +4611,7 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B151" s="2">
         <v>45717</v>
@@ -4585,12 +4620,12 @@
         <v>45747</v>
       </c>
       <c r="D151" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
       <c r="G151" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
@@ -4598,7 +4633,7 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B152" s="2">
         <v>45748</v>
@@ -4607,12 +4642,12 @@
         <v>45777</v>
       </c>
       <c r="D152" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
@@ -4620,7 +4655,7 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B153" s="2">
         <v>45778</v>
@@ -4629,12 +4664,12 @@
         <v>45808</v>
       </c>
       <c r="D153" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
@@ -4642,7 +4677,7 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B154" s="2">
         <v>45809</v>
@@ -4651,12 +4686,12 @@
         <v>45838</v>
       </c>
       <c r="D154" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
       <c r="G154" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
@@ -4664,7 +4699,7 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B155" s="2">
         <v>45839</v>
@@ -4673,12 +4708,12 @@
         <v>45869</v>
       </c>
       <c r="D155" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H155" s="3"/>
       <c r="I155" s="3"/>
@@ -4686,7 +4721,7 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B156" s="2">
         <v>45870</v>
@@ -4695,12 +4730,12 @@
         <v>45900</v>
       </c>
       <c r="D156" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
@@ -4708,7 +4743,7 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B157" s="2">
         <v>45901</v>
@@ -4717,12 +4752,12 @@
         <v>45930</v>
       </c>
       <c r="D157" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
@@ -4730,7 +4765,7 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B158" s="2">
         <v>45931</v>
@@ -4739,12 +4774,12 @@
         <v>45961</v>
       </c>
       <c r="D158" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
@@ -4752,7 +4787,7 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B159" s="2">
         <v>45962</v>
@@ -4761,12 +4796,12 @@
         <v>45991</v>
       </c>
       <c r="D159" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="G159" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H159" s="3"/>
       <c r="I159" s="3"/>
@@ -4774,7 +4809,7 @@
     </row>
     <row r="160" spans="1:10">
       <c r="A160" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B160" s="2">
         <v>45992</v>
@@ -4783,21 +4818,32 @@
         <v>46022</v>
       </c>
       <c r="D160" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="G160" s="4" t="s">
-        <v>14</v>
+        <v>336</v>
       </c>
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
       <c r="J160" s="4"/>
     </row>
+    <row r="162" spans="6:7">
+      <c r="F162" s="6">
+        <f>COUNTIF($G$5:$G$160, "done")</f>
+        <v>156</v>
+      </c>
+      <c r="G162" s="7">
+        <f>COUNTIF($G$5:$G$160, "not_started")</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="J74:J77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4813,17 +4859,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18">
-      <c r="A1" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="B1" s="7"/>
+      <c r="A1" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="9"/>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -4831,15 +4877,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28.5">
       <c r="A5" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4847,7 +4893,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4855,7 +4901,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4863,7 +4909,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4871,7 +4917,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4879,7 +4925,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4887,7 +4933,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
